--- a/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/phi-4/aae/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D3">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="H3">
         <v>426</v>
